--- a/db/templates/order_default.xlsx
+++ b/db/templates/order_default.xlsx
@@ -29,7 +29,7 @@
     <t>{{organization.postalCode}} {{organization.city}}</t>
   </si>
   <si>
-    <t>VAT: {{organization.vatin}}</t>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
   </si>
   <si>
     <t>{{organization.email}} | {{organization.phone}}</t>
@@ -62,7 +62,7 @@
     <t>{{client.postalCode}} {{client.city}}</t>
   </si>
   <si>
-    <t>VAT: {{client.vatin}}</t>
+    <t>Matricule fiscal: {{client.vatin}}</t>
   </si>
   <si>
     <t>Product</t>

--- a/db/templates/order_default.xlsx
+++ b/db/templates/order_default.xlsx
@@ -7,18 +7,21 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Order" sheetId="1" r:id="rId1"/>
+    <sheet name="Commande" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Order'!$1:$13</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Commande'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+  <si>
+    <t>{{organization.logo}}</t>
+  </si>
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -29,28 +32,10 @@
     <t>{{organization.postalCode}} {{organization.city}}</t>
   </si>
   <si>
-    <t>Matricule fiscal: {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>{{organization.email}} | {{organization.phone}}</t>
-  </si>
-  <si>
-    <t>ORDER CONFIRMATION</t>
-  </si>
-  <si>
-    <t>Order number: {{order.number}}</t>
-  </si>
-  <si>
-    <t>Order date: {{order.orderDate}}</t>
-  </si>
-  <si>
-    <t>Delivery date: {{order.deliveryDate}}</t>
-  </si>
-  <si>
-    <t>Tracking number: {{order.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Bill To</t>
+    <t>Tél : {{organization.phone}}</t>
+  </si>
+  <si>
+    <t>MF : {{organization.vatin}}</t>
   </si>
   <si>
     <t>{{client.name}}</t>
@@ -62,219 +47,279 @@
     <t>{{client.postalCode}} {{client.city}}</t>
   </si>
   <si>
-    <t>Matricule fiscal: {{client.vatin}}</t>
-  </si>
-  <si>
-    <t>Product</t>
+    <t>Tel: {{client.phone}}</t>
+  </si>
+  <si>
+    <t>CIN: {{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Commande N°: {{order.number}}</t>
+  </si>
+  <si>
+    <t>Date : {{order.orderDate}}</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Désignation</t>
+  </si>
+  <si>
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>P.U HT</t>
+  </si>
+  <si>
+    <t>TOTAL HT</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitPrice}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Total Brut HTVA</t>
+  </si>
+  <si>
+    <t>{{order.subTotal}}</t>
+  </si>
+  <si>
+    <t>Total TVA</t>
+  </si>
+  <si>
+    <t>{{order.taxTotal}}</t>
+  </si>
+  <si>
+    <t>Total TTC</t>
+  </si>
+  <si>
+    <t>{{order.total}}</t>
+  </si>
+  <si>
+    <t>Cachet et Signature</t>
+  </si>
+  <si>
+    <t>IBAN : {{organization.iban}}</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Seller logo — place alone in a cell to anchor the uploaded image there</t>
+  </si>
+  <si>
+    <t>{{order.number}}</t>
+  </si>
+  <si>
+    <t>Order number</t>
+  </si>
+  <si>
+    <t>{{order.orderDate}}</t>
+  </si>
+  <si>
+    <t>Order date</t>
+  </si>
+  <si>
+    <t>{{order.deliveryDate}}</t>
+  </si>
+  <si>
+    <t>Delivery date, blank if unset</t>
+  </si>
+  <si>
+    <t>{{order.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{order.shippingAddress}}</t>
+  </si>
+  <si>
+    <t>Free-text shipping address, blank if unset</t>
+  </si>
+  <si>
+    <t>{{order.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Tracking number, blank if unset</t>
+  </si>
+  <si>
+    <t>Seller company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Seller VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Seller email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Seller phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Seller website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Seller street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Seller house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Seller postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Seller city</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Seller IBAN</t>
+  </si>
+  <si>
+    <t>Seller bank name</t>
+  </si>
+  <si>
+    <t>Customer name</t>
+  </si>
+  <si>
+    <t>{{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Customer VAT number</t>
+  </si>
+  <si>
+    <t>{{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Customer national ID / CIN number</t>
+  </si>
+  <si>
+    <t>{{client.address}}</t>
+  </si>
+  <si>
+    <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>{{client.email}}</t>
+  </si>
+  <si>
+    <t>Customer email</t>
+  </si>
+  <si>
+    <t>{{client.phone}}</t>
+  </si>
+  <si>
+    <t>Customer phone</t>
+  </si>
+  <si>
+    <t>{{client.phone2}}</t>
+  </si>
+  <si>
+    <t>Customer phone 2</t>
+  </si>
+  <si>
+    <t>{{client.phone3}}</t>
+  </si>
+  <si>
+    <t>Customer phone 3</t>
+  </si>
+  <si>
+    <t>{{client.street}}</t>
+  </si>
+  <si>
+    <t>Customer street</t>
+  </si>
+  <si>
+    <t>{{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Customer house number</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}}</t>
+  </si>
+  <si>
+    <t>Customer postal code</t>
+  </si>
+  <si>
+    <t>{{client.city}}</t>
+  </si>
+  <si>
+    <t>Customer city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Linked product's SKU</t>
+  </si>
+  <si>
+    <t>Line item description</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Line Total</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitPrice}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>{{order.subTotal}}</t>
-  </si>
-  <si>
-    <t>Tax</t>
-  </si>
-  <si>
-    <t>{{order.taxTotal}}</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>{{order.total}}</t>
-  </si>
-  <si>
-    <t>Shipping address: {{order.shippingAddress}}</t>
-  </si>
-  <si>
-    <t>Notes: {{order.notes}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>{{order.number}}</t>
-  </si>
-  <si>
-    <t>Order number</t>
-  </si>
-  <si>
-    <t>{{order.orderDate}}</t>
-  </si>
-  <si>
-    <t>Order date</t>
-  </si>
-  <si>
-    <t>{{order.deliveryDate}}</t>
-  </si>
-  <si>
-    <t>Expected delivery date, blank if unset</t>
-  </si>
-  <si>
-    <t>{{order.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{order.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Shipment tracking number, blank if unset</t>
-  </si>
-  <si>
-    <t>Seller company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Seller VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Seller email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Seller phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Seller website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Seller street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Seller house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Seller postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Seller city</t>
-  </si>
-  <si>
-    <t>Customer name</t>
-  </si>
-  <si>
-    <t>{{client.vatin}}</t>
-  </si>
-  <si>
-    <t>Customer VAT number</t>
-  </si>
-  <si>
-    <t>{{client.email}}</t>
-  </si>
-  <si>
-    <t>Customer email</t>
-  </si>
-  <si>
-    <t>{{client.phone}}</t>
-  </si>
-  <si>
-    <t>Customer phone</t>
-  </si>
-  <si>
-    <t>{{client.street}}</t>
-  </si>
-  <si>
-    <t>Customer street</t>
-  </si>
-  <si>
-    <t>{{client.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Customer house number</t>
-  </si>
-  <si>
-    <t>{{client.postalCode}}</t>
-  </si>
-  <si>
-    <t>Customer postal code</t>
-  </si>
-  <si>
-    <t>{{client.city}}</t>
-  </si>
-  <si>
-    <t>Customer city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
-  </si>
-  <si>
-    <t>Linked product's SKU, blank on a free-text line or an unset SKU</t>
-  </si>
-  <si>
-    <t>Line item description</t>
-  </si>
-  <si>
     <t>Unit price, formatted with currency</t>
   </si>
   <si>
@@ -287,18 +332,12 @@
     <t>Subtotal before tax, computed from line items</t>
   </si>
   <si>
-    <t>Total tax — always 0.00, order line items carry no tax rate</t>
+    <t>Total tax (always zero — orders carry no per-line tax)</t>
   </si>
   <si>
     <t>Grand total, computed from line items</t>
   </si>
   <si>
-    <t>{{order.shippingAddress}}</t>
-  </si>
-  <si>
-    <t>Free-text shipping address, blank if unset</t>
-  </si>
-  <si>
     <t>{{order.notes}}</t>
   </si>
   <si>
@@ -311,7 +350,7 @@
     <t>{{export.generatedDate}}</t>
   </si>
   <si>
-    <t>Date this file was exported (not the order's own date), in the organization's date format</t>
+    <t>Date this file was exported, in the organization's date format</t>
   </si>
   <si>
     <t>{{export.generatedTime}}</t>
@@ -323,14 +362,14 @@
     <t>&amp;P (page number) / &amp;N (total pages)</t>
   </si>
   <si>
-    <t>Native Excel/LibreOffice codes, not a {{}} placeholder — only work inside this sheet's own Page Layout ▸ Header/Footer, never in a regular cell, since the page count isn't known until export. The default footer already shows "Page &amp;P of &amp;N" on every page; edit it in Excel/LibreOffice's own header/footer editor to move or restyle it</t>
+    <t>Native Excel/LibreOffice codes, only work in Page Layout ▸ Header/Footer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -351,13 +390,19 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="12"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
       <color/>
       <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
@@ -374,16 +419,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -391,11 +436,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -403,22 +462,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
   </cellXfs>
@@ -694,149 +765,180 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="22"/>
-    <col customWidth="true" max="2" min="2" width="40"/>
-    <col customWidth="true" max="4" min="3" width="14"/>
-    <col customWidth="true" max="5" min="5" width="16"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="34"/>
+    <col customWidth="true" max="5" min="3" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
+      <c r="A7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="3" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
+      <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="J12" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="4" t="s">
+    </row>
+    <row r="15">
+      <c r="D15" t="s">
         <v>24</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" s="5" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="D17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="18">
-      <c r="D18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="D19" s="1" t="s">
+      <c r="D18" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>33</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:G22"/>
+  </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
@@ -855,74 +957,74 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="8" t="s">
+    <row r="4">
+      <c r="A4" s="10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
         <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
         <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
         <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
         <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
         <v>49</v>
@@ -938,63 +1040,63 @@
     </row>
     <row r="13">
       <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
         <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
         <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
         <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
         <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
         <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
         <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
         <v>66</v>
@@ -1018,52 +1120,55 @@
     </row>
     <row r="23">
       <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
         <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="s">
         <v>79</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
         <v>82</v>
@@ -1071,125 +1176,178 @@
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="s">
-        <v>87</v>
+      <c r="B35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" t="s">
-        <v>88</v>
+      <c r="A36" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="s">
-        <v>95</v>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" t="s">
-        <v>99</v>
+      <c r="A43" s="11" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A48:C48"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/order_default.xlsx
+++ b/db/templates/order_default.xlsx
@@ -7,232 +7,238 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Commande" sheetId="1" r:id="rId1"/>
+    <sheet name="Order" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Commande'!$1:$11</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Order'!$1:$13</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+  <si>
+    <t>{{organization.name}}</t>
+  </si>
+  <si>
+    <t>{{organization.street}} {{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}} {{organization.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>{{organization.email}} | {{organization.phone}}</t>
+  </si>
+  <si>
+    <t>ORDER CONFIRMATION</t>
+  </si>
+  <si>
+    <t>Order number: {{order.number}}</t>
+  </si>
+  <si>
+    <t>Order date: {{order.orderDate}}</t>
+  </si>
+  <si>
+    <t>Delivery date: {{order.deliveryDate}}</t>
+  </si>
+  <si>
+    <t>Tracking number: {{order.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Bill To</t>
+  </si>
+  <si>
+    <t>{{client.name}}</t>
+  </si>
+  <si>
+    <t>{{client.street}} {{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}} {{client.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Line Total</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitPrice}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>{{order.subTotal}}</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>{{order.taxTotal}}</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>{{order.total}}</t>
+  </si>
+  <si>
+    <t>Shipping address: {{order.shippingAddress}}</t>
+  </si>
+  <si>
+    <t>Notes: {{order.notes}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
   <si>
     <t>{{organization.logo}}</t>
   </si>
   <si>
-    <t>{{organization.name}}</t>
-  </si>
-  <si>
-    <t>{{organization.street}} {{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}} {{organization.city}}</t>
-  </si>
-  <si>
-    <t>Tél : {{organization.phone}}</t>
-  </si>
-  <si>
-    <t>MF : {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>{{client.name}}</t>
-  </si>
-  <si>
-    <t>{{client.street}} {{client.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{client.postalCode}} {{client.city}}</t>
-  </si>
-  <si>
-    <t>Tel: {{client.phone}}</t>
-  </si>
-  <si>
-    <t>CIN: {{client.identityNumber}}</t>
-  </si>
-  <si>
-    <t>Commande N°: {{order.number}}</t>
-  </si>
-  <si>
-    <t>Date : {{order.orderDate}}</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Désignation</t>
-  </si>
-  <si>
-    <t>Quantité</t>
-  </si>
-  <si>
-    <t>P.U HT</t>
-  </si>
-  <si>
-    <t>TOTAL HT</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitPrice}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Total Brut HTVA</t>
-  </si>
-  <si>
-    <t>{{order.subTotal}}</t>
-  </si>
-  <si>
-    <t>Total TVA</t>
-  </si>
-  <si>
-    <t>{{order.taxTotal}}</t>
-  </si>
-  <si>
-    <t>Total TTC</t>
-  </si>
-  <si>
-    <t>{{order.total}}</t>
-  </si>
-  <si>
-    <t>Cachet et Signature</t>
-  </si>
-  <si>
-    <t>IBAN : {{organization.iban}}</t>
+    <t>Seller logo — place alone in a cell to anchor the uploaded image there</t>
+  </si>
+  <si>
+    <t>{{order.number}}</t>
+  </si>
+  <si>
+    <t>Order number</t>
+  </si>
+  <si>
+    <t>{{order.orderDate}}</t>
+  </si>
+  <si>
+    <t>Order date</t>
+  </si>
+  <si>
+    <t>{{order.deliveryDate}}</t>
+  </si>
+  <si>
+    <t>Delivery date, blank if unset</t>
+  </si>
+  <si>
+    <t>{{order.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{order.shippingAddress}}</t>
+  </si>
+  <si>
+    <t>Free-text shipping address, blank if unset</t>
+  </si>
+  <si>
+    <t>{{order.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Tracking number, blank if unset</t>
+  </si>
+  <si>
+    <t>Seller company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Seller VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Seller email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Seller phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Seller website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Seller street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Seller house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Seller postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Seller city</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Seller IBAN</t>
   </si>
   <si>
     <t>{{organization.bankName}}</t>
   </si>
   <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>Seller logo — place alone in a cell to anchor the uploaded image there</t>
-  </si>
-  <si>
-    <t>{{order.number}}</t>
-  </si>
-  <si>
-    <t>Order number</t>
-  </si>
-  <si>
-    <t>{{order.orderDate}}</t>
-  </si>
-  <si>
-    <t>Order date</t>
-  </si>
-  <si>
-    <t>{{order.deliveryDate}}</t>
-  </si>
-  <si>
-    <t>Delivery date, blank if unset</t>
-  </si>
-  <si>
-    <t>{{order.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{order.shippingAddress}}</t>
-  </si>
-  <si>
-    <t>Free-text shipping address, blank if unset</t>
-  </si>
-  <si>
-    <t>{{order.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Tracking number, blank if unset</t>
-  </si>
-  <si>
-    <t>Seller company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Seller VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Seller email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Seller phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Seller website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Seller street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Seller house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Seller postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Seller city</t>
-  </si>
-  <si>
-    <t>{{organization.iban}}</t>
-  </si>
-  <si>
-    <t>Seller IBAN</t>
-  </si>
-  <si>
     <t>Seller bank name</t>
   </si>
   <si>
@@ -315,9 +321,6 @@
   </si>
   <si>
     <t>Line item description</t>
-  </si>
-  <si>
-    <t>Quantity</t>
   </si>
   <si>
     <t>Unit price, formatted with currency</t>
@@ -396,13 +399,13 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
-      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="14"/>
     </font>
     <font>
       <family val="2"/>
@@ -454,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -480,10 +483,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -765,180 +771,149 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="34"/>
-    <col customWidth="true" max="5" min="3" width="16"/>
+    <col customWidth="true" max="1" min="1" width="22"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
+    <col customWidth="true" max="4" min="3" width="14"/>
+    <col customWidth="true" max="5" min="5" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="s">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
     </row>
     <row r="9">
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="B13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="C13" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="5" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="B14" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J12" t="s">
+      <c r="D14" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="D15" t="s">
+      <c r="E14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F14" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18">
-      <c r="D18" s="8" t="s">
+    <row r="19">
+      <c r="D19" s="1" t="s">
         <v>30</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:G22"/>
-  </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
@@ -957,388 +932,388 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>33</v>
+      <c r="A1" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>34</v>
+      <c r="A2" s="13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>37</v>
       </c>
+      <c r="C4" s="11" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="s">
-        <v>95</v>
+      <c r="A36" s="12" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="s">
-        <v>102</v>
+      <c r="A43" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="s">
-        <v>108</v>
+      <c r="A48" s="12" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C49" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/db/templates/order_default.xlsx
+++ b/db/templates/order_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -56,7 +56,7 @@
     <t>{{client.name}}</t>
   </si>
   <si>
-    <t>{{client.street}} {{client.houseNumber}}</t>
+    <t>{{client.addressLine}}</t>
   </si>
   <si>
     <t>{{client.postalCode}} {{client.city}}</t>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>Customer street and house number, or the single-line address when there is no street</t>
   </si>
   <si>
     <t>{{client.email}}</t>
@@ -1135,84 +1138,84 @@
     </row>
     <row r="28">
       <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
         <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
         <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s">
         <v>85</v>
-      </c>
-      <c r="C30" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" t="s">
         <v>87</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" t="s">
         <v>89</v>
-      </c>
-      <c r="C32" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" t="s">
         <v>91</v>
-      </c>
-      <c r="C33" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s">
         <v>93</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
         <v>95</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="36">
+      <c r="B36" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="s">
+      <c r="C36" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="A37" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
         <v>99</v>
@@ -1220,7 +1223,7 @@
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
         <v>100</v>
@@ -1228,44 +1231,44 @@
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="s">
+      <c r="B43" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="s">
-        <v>27</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="A44" s="12" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
         <v>105</v>
@@ -1273,7 +1276,7 @@
     </row>
     <row r="46">
       <c r="B46" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
         <v>106</v>
@@ -1281,48 +1284,56 @@
     </row>
     <row r="47">
       <c r="B47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" t="s">
         <v>107</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="48">
+      <c r="B48" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="s">
+      <c r="C48" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="s">
+      <c r="A49" s="12" t="s">
         <v>110</v>
-      </c>
-      <c r="C49" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" t="s">
         <v>112</v>
-      </c>
-      <c r="C50" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s">
         <v>114</v>
       </c>
-      <c r="C51" t="s">
+    </row>
+    <row r="52">
+      <c r="B52" t="s">
         <v>115</v>
+      </c>
+      <c r="C52" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A49:C49"/>
   </mergeCells>
 </worksheet>
 </file>